--- a/DATA reporting_practices - ANOVA rep.xlsx
+++ b/DATA reporting_practices - ANOVA rep.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Data Replication Centre\Joe Reporting Practices Paper\reporting_practices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F63700-BD1D-4935-BF41-23182E354D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992723E5-B945-467E-B870-DAFC26D832D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="16185" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6310,7 +6310,7 @@
         <v>0.05</v>
       </c>
       <c r="K86" s="34">
-        <v>5.0000999999999997E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="L86" s="28">
         <v>0.99417612177734904</v>
